--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA2629D-3B83-41D9-A0C4-D52B3D31D789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA22D82-84E8-48A3-ADD4-AB38F407E6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16416" yWindow="2832" windowWidth="25068" windowHeight="17916" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="5736" windowWidth="24612" windowHeight="17532" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
   <si>
     <t>Table Name</t>
   </si>
@@ -186,6 +186,9 @@
     <t>Insert Exclude</t>
   </si>
   <si>
+    <t>Insert SQL Expression</t>
+  </si>
+  <si>
     <t>Start Value</t>
   </si>
   <si>
@@ -213,6 +216,12 @@
     <t>nextAlphaNumeric( 20 )</t>
   </si>
   <si>
+    <t>nextAlphaNumeric( 12 )</t>
+  </si>
+  <si>
+    <t>Max Value</t>
+  </si>
+  <si>
     <t>addMonths(_start.DATE_COL,1)</t>
   </si>
   <si>
@@ -222,6 +231,9 @@
     <t>Next Value</t>
   </si>
   <si>
+    <t>addDays(_previous.DATE_COL,1)</t>
+  </si>
+  <si>
     <t>addSeconds(_previous.TIME_COL,1)</t>
   </si>
   <si>
@@ -252,53 +264,52 @@
     <t>_previous.INTEGER_VALUES_COL + 1</t>
   </si>
   <si>
+    <t>_previous.NUMERIC_VALUES_COL + 1</t>
+  </si>
+  <si>
+    <t>_previous.INTEGER_GROUP_COL + 1</t>
+  </si>
+  <si>
     <t>Values</t>
   </si>
   <si>
     <t>SELECT　SQL</t>
   </si>
   <si>
-    <t>abc</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>def</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>ghi</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>Group1</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>SELECT 1 AS INTEGER_GROUP_COL, 'XXX' AS VARCHAR_GROUP_COL  FROM (VALUES(0))
-UNION ALL
-SELECT 1 AS INTEGER_GROUP_COL, 'XXX' AS VARCHAR_GROUP_COL  FROM (VALUES(0))</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>Max Value</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>addDays(_previous.DATE_COL,1)</t>
-    <phoneticPr fontId="20"/>
+    <t>VARCHAR_EXPRESSION</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>'abc'</t>
+    <phoneticPr fontId="23"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
@@ -451,7 +462,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,34 +502,40 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -858,37 +875,38 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="32.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="29.09765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="44.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="44" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.09765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -949,8 +967,11 @@
       <c r="T1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="U1" s="23" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -1011,8 +1032,11 @@
       <c r="T2" s="6" t="s">
         <v>35</v>
       </c>
+      <c r="U2" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
         <v>36</v>
       </c>
@@ -1067,14 +1091,17 @@
       <c r="R3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" t="s">
-        <v>66</v>
+      <c r="S3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>38</v>
       </c>
@@ -1135,214 +1162,278 @@
       <c r="T4" s="10" t="b">
         <v>0</v>
       </c>
+      <c r="U4" s="10" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A5" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" s="24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="C6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="12">
+      <c r="D6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="14">
         <v>1</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F6" s="14">
         <v>1</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G6" s="14">
         <v>1</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H6" s="14">
         <v>1</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I6" s="14">
         <v>1</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="M6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="12">
+      <c r="N6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="14">
         <v>1</v>
       </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12" t="s">
+      <c r="P6" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="14">
+        <v>1</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" s="14"/>
+    </row>
+    <row r="7" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="16">
+        <v>127</v>
+      </c>
+      <c r="F7" s="16">
+        <v>32767</v>
+      </c>
+      <c r="G7" s="16">
+        <v>2147483647</v>
+      </c>
+      <c r="H7" s="16">
+        <v>9.2233720368547758E+18</v>
+      </c>
+      <c r="I7" s="16">
+        <v>100</v>
+      </c>
+      <c r="J7" s="16">
+        <v>1.7976931348623157E+308</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1.7976931348623157E+308</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16">
+        <v>2147483647</v>
+      </c>
+      <c r="P7" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>1.7976931348623157E+308</v>
+      </c>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16">
+        <v>2147483647</v>
+      </c>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+    </row>
+    <row r="8" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
+      <c r="O8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="R8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" s="18"/>
     </row>
-    <row r="6" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
-      <c r="A6" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="13">
-        <v>127</v>
-      </c>
-      <c r="F6" s="13">
-        <v>32767</v>
-      </c>
-      <c r="G6" s="13">
-        <v>2147483647</v>
-      </c>
-      <c r="H6" s="13">
-        <v>9.2233720368547758E+18</v>
-      </c>
-      <c r="I6" s="13">
-        <v>100</v>
-      </c>
-      <c r="J6" s="13">
-        <v>1.7976931348623157E+308</v>
-      </c>
-      <c r="K6" s="13">
-        <v>1.7976931348623157E+308</v>
-      </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13">
-        <v>2147483647</v>
-      </c>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-    </row>
-    <row r="7" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
-      <c r="A7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-    </row>
-    <row r="8" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
-      <c r="A8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17">
-        <v>1000.123</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>1.17</v>
-      </c>
-      <c r="R8" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-    </row>
-    <row r="9" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="20"/>
-      <c r="P9" s="20">
-        <v>1111.2339999999999</v>
-      </c>
-      <c r="Q9">
-        <v>1.18</v>
-      </c>
-      <c r="R9" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="23.4" x14ac:dyDescent="0.4">
-      <c r="P10" s="20">
-        <v>2222.3449999999998</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>1.19</v>
-      </c>
-      <c r="R10" s="20" t="s">
-        <v>65</v>
-      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -1350,31 +1441,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:1" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>67</v>
+    <row r="2" spans="1:1" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3185659F-FB4C-4203-95A7-328D430561B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1DE791-FC02-4C78-ABF4-2AA21A4E35E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="5736" windowWidth="24612" windowHeight="17532" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="5736" windowWidth="24612" windowHeight="17532" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="71">
   <si>
     <t>Table Name</t>
   </si>
@@ -219,9 +219,6 @@
     <t>nextAlphaNumeric( 20 )</t>
   </si>
   <si>
-    <t>nextAlphaNumeric( 12 )</t>
-  </si>
-  <si>
     <t>Max Value</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>_previous.NUMERIC_VALUES_COL + 1</t>
   </si>
   <si>
-    <t>_previous.INTEGER_GROUP_COL + 1</t>
-  </si>
-  <si>
     <t>Values</t>
   </si>
   <si>
@@ -280,6 +274,18 @@
   </si>
   <si>
     <t>'abc'</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>Group1</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>SELECT 123 AS INTEGER_GROUP_COL, 'abc123' AS VARCHAR_GROUP_COL FROM (VALUES(0))
+UNION ALL
+SELECT 456 AS INTEGER_GROUP_COL, 'abc456' AS VARCHAR_GROUP_COL FROM (VALUES(0))
+UNION ALL
+SELECT 789 AS INTEGER_GROUP_COL, 'abc789' AS VARCHAR_GROUP_COL FROM (VALUES(0))</t>
     <phoneticPr fontId="23"/>
   </si>
 </sst>
@@ -461,7 +467,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,6 +539,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,14 +1095,11 @@
       <c r="R3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>38</v>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
@@ -1216,14 +1222,10 @@
       <c r="R5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" s="12" t="s">
-        <v>38</v>
-      </c>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
       <c r="U5" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
@@ -1281,24 +1283,20 @@
       <c r="R6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="S6" s="14">
-        <v>1</v>
-      </c>
-      <c r="T6" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
       <c r="U6" s="14"/>
     </row>
     <row r="7" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>52</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="16">
         <v>127</v>
@@ -1334,48 +1332,46 @@
         <v>1.7976931348623157E+308</v>
       </c>
       <c r="R7" s="16"/>
-      <c r="S7" s="16">
-        <v>2147483647</v>
-      </c>
+      <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
     </row>
     <row r="8" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="F8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="G8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="H8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="I8" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="J8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="K8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>63</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>64</v>
       </c>
       <c r="M8" s="18" t="s">
         <v>47</v>
@@ -1384,28 +1380,24 @@
         <v>48</v>
       </c>
       <c r="O8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="18" t="s">
-        <v>66</v>
-      </c>
       <c r="Q8" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="T8" s="18" t="s">
-        <v>50</v>
-      </c>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
       <c r="U8" s="18"/>
     </row>
     <row r="9" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -1437,20 +1429,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
         <v>37</v>
       </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" ht="23.4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="144" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1DE791-FC02-4C78-ABF4-2AA21A4E35E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C2539A-932D-4833-BFF8-965A3EEC25A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="5736" windowWidth="24612" windowHeight="17532" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15216" yWindow="5988" windowWidth="24612" windowHeight="17532" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>Table Name</t>
   </si>
@@ -286,6 +286,18 @@
 SELECT 456 AS INTEGER_GROUP_COL, 'abc456' AS VARCHAR_GROUP_COL FROM (VALUES(0))
 UNION ALL
 SELECT 789 AS INTEGER_GROUP_COL, 'abc789' AS VARCHAR_GROUP_COL FROM (VALUES(0))</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>abc</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>def</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>ghi</t>
     <phoneticPr fontId="23"/>
   </si>
 </sst>
@@ -467,7 +479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -542,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -887,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.3984375" bestFit="1" customWidth="1"/>
@@ -1420,6 +1435,48 @@
       <c r="T9" s="20"/>
       <c r="U9" s="20"/>
     </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="O11" s="25">
+        <v>2</v>
+      </c>
+      <c r="P11" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>1.2</v>
+      </c>
+      <c r="R11" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="23.4" x14ac:dyDescent="0.4">
+      <c r="O12" s="25">
+        <v>3</v>
+      </c>
+      <c r="P12" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="R12" s="25" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C2539A-932D-4833-BFF8-965A3EEC25A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E112B3EA-3672-45AE-B6E0-1E8EE3FCF1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15216" yWindow="5988" windowWidth="24612" windowHeight="17532" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8664" yWindow="2784" windowWidth="24816" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
   <si>
     <t>Table Name</t>
   </si>
@@ -298,6 +298,18 @@
   </si>
   <si>
     <t>ghi</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>Setup SQL</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>Finalize SQL</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM TAB1</t>
     <phoneticPr fontId="23"/>
   </si>
 </sst>
@@ -479,7 +491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -556,6 +568,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -872,10 +887,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.4">
@@ -892,6 +908,22 @@
       </c>
       <c r="B2" s="2">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C01A22-DC6E-4E29-9463-A796C110021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD10E35A-345A-4D86-A7E3-79C7E1D1EC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8664" yWindow="2784" windowWidth="24816" windowHeight="19800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14040" yWindow="3672" windowWidth="24816" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
     <sheet name="Column" sheetId="2" r:id="rId2"/>
-    <sheet name="QueryDefinition" sheetId="3" r:id="rId3"/>
+    <sheet name="Query" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>Table Name</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>TAB1</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM PUBLIC.TAB1</t>
   </si>
   <si>
     <t>Column Name</t>
@@ -375,68 +372,54 @@
   </si>
   <si>
     <t>Group1</t>
-    <phoneticPr fontId="197"/>
+    <phoneticPr fontId="189"/>
   </si>
   <si>
     <t>'abc'</t>
-    <phoneticPr fontId="197"/>
+    <phoneticPr fontId="189"/>
   </si>
   <si>
     <t>abc</t>
-    <phoneticPr fontId="197"/>
+    <phoneticPr fontId="189"/>
   </si>
   <si>
     <t>def</t>
-    <phoneticPr fontId="197"/>
+    <phoneticPr fontId="189"/>
   </si>
   <si>
     <t>gh1</t>
-    <phoneticPr fontId="197"/>
+    <phoneticPr fontId="189"/>
+  </si>
+  <si>
+    <t>Start Value SQL</t>
+  </si>
+  <si>
+    <t>SELECT
+	TINYINT_COL + 1 AS TINYINT_COL
+	, SMALLINT_COL + 1 AS SMALLINT_COL
+	, INTEGER_COL + 1 AS INTEGER_COL
+	, BIGINT_COL + 1 AS BIGINT_COL
+	, NUMERIC_COL + 1 AS NUMERIC_COL
+	, INTEGER_VALUES_COL + 1 AS INTEGER_VALUES_COL
+	, NUMERIC_VALUES_COL + 1 AS NUMERIC_VALUES_COL
+	, INTEGER_GROUP_COL + 1 AS INTEGER_GROUP_COL
+FROM TAB1</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM TAB1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="199" x14ac:knownFonts="1">
+  <fonts count="191" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1203,7 +1186,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1218,6 +1201,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1261,7 +1249,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1277,589 +1265,568 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="187" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="188" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="190" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2176,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
@@ -2187,43 +2154,51 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="192" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>100</v>
+      <c r="B2" s="192">
+        <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
+    <row r="3" spans="1:2" ht="187.2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>5</v>
+      <c r="B5" s="192" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="197"/>
+  <phoneticPr fontId="189"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:AM21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
@@ -2237,348 +2212,378 @@
     <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
+      <c r="B2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="18"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21" t="b">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="26"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="27"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30" t="b">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A4" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="35"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="36"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="39" t="b">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A5" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="44"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="45"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="46" t="s">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A6" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48" t="b">
+      <c r="G6" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="54"/>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A7" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="53"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="63"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="57" t="b">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A8" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="66"/>
+      <c r="D8" s="67" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="62"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="72"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" s="63" t="s">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A9" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="81"/>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A10" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="84"/>
+      <c r="D10" s="85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="86"/>
+      <c r="F10" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="89" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="90"/>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A11" s="91" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="95"/>
+      <c r="F11" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="98" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="99"/>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A12" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="101" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="102"/>
+      <c r="D12" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="106"/>
+      <c r="H12" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="108"/>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A13" s="109" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="111"/>
+      <c r="D13" s="112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="113"/>
+      <c r="F13" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="115"/>
+      <c r="H13" s="116" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="117"/>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A14" s="118" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="122"/>
+      <c r="F14" s="123" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="124"/>
+      <c r="H14" s="125" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="126"/>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A15" s="127" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="C15" s="129"/>
+      <c r="D15" s="130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="131"/>
+      <c r="F15" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="67"/>
-      <c r="F7" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="71"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="74"/>
-      <c r="D8" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="77" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="80"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="81" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="87" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="88" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="89"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="90" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="95" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="98"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" s="99" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="103"/>
-      <c r="F11" s="104" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="105" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="106" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="107"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" s="108" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="109" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="112"/>
-      <c r="F12" s="113" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="114"/>
-      <c r="H12" s="115" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="116"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="117" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="118" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="121"/>
-      <c r="F13" s="122" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="123"/>
-      <c r="H13" s="124" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="125"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="126" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="127" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="128"/>
-      <c r="D14" s="129" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="130"/>
-      <c r="F14" s="131" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="132"/>
-      <c r="H14" s="133" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="134"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="135" t="s">
+      <c r="H15" s="134" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="136" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="137"/>
-      <c r="D15" s="138" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="139"/>
-      <c r="F15" s="140" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="141" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="142" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="143">
+      <c r="I15" s="135">
         <v>123</v>
       </c>
       <c r="J15">
@@ -2588,28 +2593,28 @@
         <v>789</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" s="144" t="s">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="A16" s="136" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="137" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="140"/>
+      <c r="F16" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="145" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="147" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="148"/>
-      <c r="F16" s="149" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="150" t="s">
+      <c r="H16" s="143" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="151" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="143">
+      <c r="I16" s="135">
         <v>123</v>
       </c>
       <c r="J16">
@@ -2620,27 +2625,27 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="152" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="153" t="s">
+      <c r="A17" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="145" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="146"/>
+      <c r="D17" s="147" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="148"/>
+      <c r="F17" s="149" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="154"/>
-      <c r="D17" s="155" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="157" t="s">
+      <c r="G17" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="158" t="s">
+      <c r="H17" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="159" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="160">
+      <c r="I17" s="152">
         <v>1.2</v>
       </c>
       <c r="J17">
@@ -2651,107 +2656,107 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="161" t="s">
+      <c r="A18" s="153" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="155"/>
+      <c r="D18" s="156" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="157"/>
+      <c r="F18" s="158" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="162" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="163"/>
-      <c r="D18" s="164" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="165"/>
-      <c r="F18" s="166" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="167"/>
-      <c r="H18" s="168" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="197" t="s">
+      <c r="G18" s="159"/>
+      <c r="H18" s="160" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="189" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="191" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="199" t="s">
+      <c r="K18" s="191" t="s">
         <v>85</v>
-      </c>
-      <c r="K18" s="199" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A19" s="169" t="s">
+      <c r="A19" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="162" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="163" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="164" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="165"/>
+      <c r="F19" s="166" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="168" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="170" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="171" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="173"/>
-      <c r="F19" s="174" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="175" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="176" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="177"/>
+      <c r="I19" s="169"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="178" t="s">
+      <c r="A20" s="170" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="171" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="163" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="172" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="173"/>
+      <c r="F20" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="179" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="171" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="180" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="181"/>
-      <c r="F20" s="182" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="183"/>
-      <c r="H20" s="184" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="185"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="176" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="177"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" s="186" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="187" t="s">
+      <c r="A21" s="178" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="179" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="180"/>
+      <c r="D21" s="181" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="190" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="188"/>
-      <c r="D21" s="189" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="198" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="190" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="191"/>
-      <c r="H21" s="192" t="s">
-        <v>65</v>
-      </c>
-      <c r="I21" s="193"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="184" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="185"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="197"/>
+  <phoneticPr fontId="189"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -2767,23 +2772,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="194" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="195" t="s">
-        <v>79</v>
+      <c r="A1" s="186" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="187" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="330" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="197" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="196" t="s">
+      <c r="A2" s="189" t="s">
         <v>81</v>
+      </c>
+      <c r="B2" s="188" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="197"/>
+  <phoneticPr fontId="189"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD10E35A-345A-4D86-A7E3-79C7E1D1EC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832CA083-764C-4E8F-8F07-E96FE7DF4063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14040" yWindow="3672" windowWidth="24816" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="2472" windowWidth="24816" windowHeight="19800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
   <si>
     <t>Table Name</t>
   </si>
@@ -129,12 +129,6 @@
   </si>
   <si>
     <t>Generation Group</t>
-  </si>
-  <si>
-    <t>Insert Exclude</t>
-  </si>
-  <si>
-    <t>Insert SQL Expression</t>
   </si>
   <si>
     <t>Start Value</t>
@@ -372,23 +366,19 @@
   </si>
   <si>
     <t>Group1</t>
-    <phoneticPr fontId="189"/>
-  </si>
-  <si>
-    <t>'abc'</t>
-    <phoneticPr fontId="189"/>
+    <phoneticPr fontId="148"/>
   </si>
   <si>
     <t>abc</t>
-    <phoneticPr fontId="189"/>
+    <phoneticPr fontId="148"/>
   </si>
   <si>
     <t>def</t>
-    <phoneticPr fontId="189"/>
+    <phoneticPr fontId="148"/>
   </si>
   <si>
     <t>gh1</t>
-    <phoneticPr fontId="189"/>
+    <phoneticPr fontId="148"/>
   </si>
   <si>
     <t>Start Value SQL</t>
@@ -408,182 +398,71 @@
   <si>
     <t>SELECT COUNT(*) FROM TAB1</t>
   </si>
+  <si>
+    <t>Insert SQL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT INTO PUBLIC.TAB1 
+(
+	  DATE_COL
+	, TIME_COL
+	, TIMESTAMP_COL
+	, TINYINT_COL
+	, SMALLINT_COL
+	, INTEGER_COL
+	, BIGINT_COL
+	, NUMERIC_COL
+	, FLOAT_COL
+	, DOUBLE_COL
+	, BOOLEAN_COL
+	, CHAR_COL
+	, VARCHAR_COL
+	, INTEGER_VALUES_COL
+	, NUMERIC_VALUES_COL
+	, DOUBLE_VALUES_COL
+	, VARCHAR_VALUES_COL
+	, INTEGER_GROUP_COL
+	, VARCHAR_GROUP_COL
+	, VARCHAR_EXPRESSION
+)
+VALUES
+(
+	  /*DATE_COL*/CURRENT_DATE
+	, /*TIME_COL*/LOCALTIME
+	, /*TIMESTAMP_COL*/LOCALTIMESTAMP
+	, /*TINYINT_COL*/0
+	, /*SMALLINT_COL*/0
+	, /*INTEGER_COL*/0
+	, /*BIGINT_COL*/0
+	, /*NUMERIC_COL*/0
+	, /*FLOAT_COL*/0.0
+	, /*DOUBLE_COL*/0.0
+	, /*BOOLEAN_COL*/FALSE
+	, /*CHAR_COL*/''
+	, /*VARCHAR_COL*/''
+	, /*INTEGER_VALUES_COL*/0
+	, /*NUMERIC_VALUES_COL*/0
+	, /*DOUBLE_VALUES_COL*/0.0
+	, /*VARCHAR_VALUES_COL*/''
+	, /*INTEGER_GROUP_COL*/0
+	, /*VARCHAR_GROUP_COL*/''
+	, 'abc'
+)
+</t>
+    <phoneticPr fontId="148"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="191" x14ac:knownFonts="1">
+  <fonts count="150" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1249,7 +1128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1274,559 +1153,436 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="146" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="147" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="149" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2143,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
@@ -2154,7 +1910,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="192" t="s">
+      <c r="B1" s="150" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2162,57 +1918,63 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="192">
+      <c r="B2" s="150">
         <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="187.2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="192" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="B3" s="150" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="192" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B4" s="150" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="151" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="192" t="s">
-        <v>88</v>
+      <c r="B6" s="150" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="189"/>
+  <phoneticPr fontId="148"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -2231,15 +1993,11 @@
       <c r="F1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2268,495 +2026,411 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A3" s="19" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24" t="s">
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="27"/>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="C4" s="24"/>
+      <c r="D4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="E4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="28"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A5" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="B5" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="36"/>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A5" s="37" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="E5" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="35"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A6" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="B6" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="F6" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A7" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="B7" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="54"/>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A7" s="55" t="s">
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="F7" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A8" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="B8" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="63"/>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A8" s="64" t="s">
+      <c r="C8" s="52"/>
+      <c r="D8" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="F8" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="70" t="s">
+      <c r="G8" s="56"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A9" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="71" t="s">
+      <c r="B9" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="72"/>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A9" s="73" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="F9" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="63"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A10" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="B10" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="81"/>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A10" s="82" t="s">
+      <c r="C10" s="66"/>
+      <c r="D10" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="E10" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="85" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="86"/>
-      <c r="F10" s="87" t="s">
+      <c r="F10" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="G10" s="70"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A11" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="89" t="s">
+      <c r="B11" s="72" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="77"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A12" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="90"/>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A11" s="91" t="s">
+      <c r="B12" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="C12" s="80"/>
+      <c r="D12" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="82"/>
+      <c r="F12" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="84"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A13" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="89"/>
+      <c r="F13" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="91"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A14" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="94"/>
+      <c r="D14" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="96"/>
+      <c r="F14" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="98"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A15" s="99" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="105">
+        <v>123</v>
+      </c>
+      <c r="H15">
+        <v>456</v>
+      </c>
+      <c r="I15">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A16" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="105">
+        <v>123</v>
+      </c>
+      <c r="H16">
+        <v>456</v>
+      </c>
+      <c r="I16">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="96" t="s">
+      <c r="F17" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="97" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="98" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="99"/>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A12" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="101" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="106"/>
-      <c r="H12" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="108"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A13" s="109" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="113"/>
-      <c r="F13" s="114" t="s">
+      <c r="G17" s="118">
+        <v>1.2</v>
+      </c>
+      <c r="H17">
+        <v>1.3</v>
+      </c>
+      <c r="I17">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="119" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="115"/>
-      <c r="H13" s="116" t="s">
+      <c r="C18" s="121"/>
+      <c r="D18" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="123"/>
+      <c r="F18" s="124" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="149" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" s="149" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="127" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="128" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="129" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="131"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="117"/>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A14" s="118" t="s">
+      <c r="C20" s="127" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="134" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="135"/>
+      <c r="F20" s="136" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="137"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="139" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="140"/>
+      <c r="D21" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="119" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="121" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="122"/>
-      <c r="F14" s="123" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="124"/>
-      <c r="H14" s="125" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="126"/>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A15" s="127" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="128" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="129"/>
-      <c r="D15" s="130" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="131"/>
-      <c r="F15" s="132" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="133" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="134" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="135">
-        <v>123</v>
-      </c>
-      <c r="J15">
-        <v>456</v>
-      </c>
-      <c r="K15">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A16" s="136" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="137" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="139" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="140"/>
-      <c r="F16" s="141" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="142" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="143" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="135">
-        <v>123</v>
-      </c>
-      <c r="J16">
-        <v>456</v>
-      </c>
-      <c r="K16">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="144" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="145" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="146"/>
-      <c r="D17" s="147" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="148"/>
-      <c r="F17" s="149" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="150" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" s="151" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="152">
-        <v>1.2</v>
-      </c>
-      <c r="J17">
-        <v>1.3</v>
-      </c>
-      <c r="K17">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="153" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="154" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="155"/>
-      <c r="D18" s="156" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="157"/>
-      <c r="F18" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="159"/>
-      <c r="H18" s="160" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="189" t="s">
-        <v>83</v>
-      </c>
-      <c r="J18" s="191" t="s">
-        <v>84</v>
-      </c>
-      <c r="K18" s="191" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A19" s="161" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="162" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="163" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="164" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="165"/>
-      <c r="F19" s="166" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="167" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" s="168" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" s="169"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="170" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="171" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="163" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="173"/>
-      <c r="F20" s="174" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="175"/>
-      <c r="H20" s="176" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="177"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" s="178" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="179" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="180"/>
-      <c r="D21" s="181" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="182" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="183"/>
-      <c r="H21" s="184" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="185"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="143" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="144"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="189"/>
+  <phoneticPr fontId="148"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -2772,23 +2446,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="187" t="s">
+      <c r="B1" s="146" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="330" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="148" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="147" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="330" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="189" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="188" t="s">
-        <v>80</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="189"/>
+  <phoneticPr fontId="148"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832CA083-764C-4E8F-8F07-E96FE7DF4063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4F77D1-A011-4A20-B327-BF67387BB0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="2472" windowWidth="24816" windowHeight="19800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24072" yWindow="2940" windowWidth="20712" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -384,18 +384,6 @@
     <t>Start Value SQL</t>
   </si>
   <si>
-    <t>SELECT
-	TINYINT_COL + 1 AS TINYINT_COL
-	, SMALLINT_COL + 1 AS SMALLINT_COL
-	, INTEGER_COL + 1 AS INTEGER_COL
-	, BIGINT_COL + 1 AS BIGINT_COL
-	, NUMERIC_COL + 1 AS NUMERIC_COL
-	, INTEGER_VALUES_COL + 1 AS INTEGER_VALUES_COL
-	, NUMERIC_VALUES_COL + 1 AS NUMERIC_VALUES_COL
-	, INTEGER_GROUP_COL + 1 AS INTEGER_GROUP_COL
-FROM TAB1</t>
-  </si>
-  <si>
     <t>SELECT COUNT(*) FROM TAB1</t>
   </si>
   <si>
@@ -451,6 +439,12 @@
 </t>
     <phoneticPr fontId="148"/>
   </si>
+  <si>
+    <t>SELECT
+	COALESCE( MAX( INTEGER_COL + 1 ),  1 ) AS INTEGER_COL
+FROM TAB1</t>
+    <phoneticPr fontId="148"/>
+  </si>
 </sst>
 </file>
 
@@ -467,590 +461,737 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1916,34 +2057,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="150">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="187.2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="B2" s="150" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B3" s="150" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="150" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="B4" s="150">
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="151" t="s">
         <v>86</v>
-      </c>
-      <c r="B5" s="151" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -1951,7 +2092,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/TAB1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4F77D1-A011-4A20-B327-BF67387BB0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A54E98-143A-49A0-9473-C78547010D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24072" yWindow="2940" windowWidth="20712" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7272" yWindow="1596" windowWidth="22524" windowHeight="17364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -105,20 +105,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>Table Name</t>
   </si>
   <si>
-    <t>Number of Rows</t>
-  </si>
-  <si>
-    <t>Setup SQL</t>
-  </si>
-  <si>
-    <t>Finalize SQL</t>
-  </si>
-  <si>
     <t>TAB1</t>
   </si>
   <si>
@@ -131,9 +122,6 @@
     <t>Generation Group</t>
   </si>
   <si>
-    <t>Start Value</t>
-  </si>
-  <si>
     <t>Max Value</t>
   </si>
   <si>
@@ -149,12 +137,6 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>LocalDate.of(2025,3,1)</t>
-  </si>
-  <si>
-    <t>addMonths(_start.DATE_COL,1)</t>
-  </si>
-  <si>
     <t>addDays(_previous.DATE_COL,1)</t>
   </si>
   <si>
@@ -174,12 +156,6 @@
   </si>
   <si>
     <t>TIMESTAMP</t>
-  </si>
-  <si>
-    <t>LocalDateTime.of(2025,3,1,0,0,0)</t>
-  </si>
-  <si>
-    <t>addMonths(_start.TIMESTAMP_COL,1)</t>
   </si>
   <si>
     <t>addMilliSeconds(_previous.TIMESTAMP_COL,1)</t>
@@ -366,28 +342,22 @@
   </si>
   <si>
     <t>Group1</t>
-    <phoneticPr fontId="148"/>
+    <phoneticPr fontId="87"/>
   </si>
   <si>
     <t>abc</t>
-    <phoneticPr fontId="148"/>
+    <phoneticPr fontId="87"/>
   </si>
   <si>
     <t>def</t>
-    <phoneticPr fontId="148"/>
+    <phoneticPr fontId="87"/>
   </si>
   <si>
     <t>gh1</t>
-    <phoneticPr fontId="148"/>
-  </si>
-  <si>
-    <t>Start Value SQL</t>
+    <phoneticPr fontId="87"/>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM TAB1</t>
-  </si>
-  <si>
-    <t>Insert SQL</t>
   </si>
   <si>
     <t xml:space="preserve">INSERT INTO PUBLIC.TAB1 
@@ -437,331 +407,70 @@
 	, 'abc'
 )
 </t>
-    <phoneticPr fontId="148"/>
+    <phoneticPr fontId="87"/>
+  </si>
+  <si>
+    <t>Min Value</t>
+    <phoneticPr fontId="87"/>
+  </si>
+  <si>
+    <t>①Setup SQL
+[1 execution]</t>
+  </si>
+  <si>
+    <t>②Start Value
+[1 execution]</t>
+  </si>
+  <si>
+    <t>③Number of Rows</t>
+  </si>
+  <si>
+    <t>④Insert SQL
+[②×③ execution]</t>
+  </si>
+  <si>
+    <t>④Finalize SQL
+[1 execution]</t>
+  </si>
+  <si>
+    <t>LocalDate.of(2025,4,1)</t>
+  </si>
+  <si>
+    <t>addMonths(_min.DATE_COL,1)</t>
+  </si>
+  <si>
+    <t>LocalDateTime.of(2025,4,1,0,0,0)</t>
+  </si>
+  <si>
+    <t>addMonths(_min.TIMESTAMP_COL,1)</t>
   </si>
   <si>
     <t>SELECT
-	COALESCE( MAX( INTEGER_COL + 1 ),  1 ) AS INTEGER_COL
+	COALESCE( MAX( INTEGER_COL ),  0 ) AS INTEGER_COL
+FROM TAB1
+UNION ALL
+SELECT
+	COALESCE( MAX( INTEGER_COL + 1 ),  2) AS INTEGER_COL
 FROM TAB1</t>
-    <phoneticPr fontId="148"/>
+    <phoneticPr fontId="87"/>
+  </si>
+  <si>
+    <t>TRUNCATE TABLE TAB1;
+SELECT COUNT(*) FROM TAB1</t>
+    <phoneticPr fontId="87"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="150" x14ac:knownFonts="1">
+  <fonts count="89" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1269,7 +978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1291,439 +1000,256 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="85" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2040,63 +1566,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B1" s="89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="150" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="129.6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="150" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="89" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C3" s="89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="150">
+        <v>80</v>
+      </c>
+      <c r="B4" s="89">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="151" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+      <c r="B5" s="90" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="150" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="148"/>
+  <phoneticPr fontId="87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2109,7 +1639,7 @@
     <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.09765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.09765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.19921875" bestFit="1" customWidth="1"/>
@@ -2117,25 +1647,25 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2169,262 +1699,262 @@
       <c r="AK1" s="1"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="89" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11" t="s">
+      <c r="E3" s="89"/>
+      <c r="F3" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="B4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A4" s="22" t="s">
+      <c r="E5" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="F5" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="G5" s="22"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="28"/>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A5" s="29" t="s">
+      <c r="F6" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A7" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32" t="s">
+      <c r="B7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="C7" s="29"/>
+      <c r="D7" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F7" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="35"/>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A6" s="36" t="s">
+      <c r="G7" s="30"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A8" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B8" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39" t="s">
+      <c r="C8" s="33"/>
+      <c r="D8" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="89" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="89" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A9" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="89" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="89" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A10" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="41"/>
+      <c r="D10" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="42"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A11" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="46"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A12" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="89" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="50"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A13" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="53"/>
+      <c r="D13" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="54"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A14" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="58"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A15" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A7" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="49"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A8" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="56"/>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A9" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="63"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A10" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="70"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A11" s="71" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="74" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="76" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="77"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A12" s="78" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="79" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="82"/>
-      <c r="F12" s="83" t="s">
+      <c r="C15" s="61"/>
+      <c r="D15" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="84"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A13" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="89"/>
-      <c r="F13" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="91"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A14" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="94"/>
-      <c r="D14" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="96"/>
-      <c r="F14" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="98"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A15" s="99" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="100" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="101"/>
-      <c r="D15" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="103" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="105">
+      <c r="G15" s="62">
         <v>123</v>
       </c>
       <c r="H15">
@@ -2435,23 +1965,23 @@
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A16" s="106" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="109" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="111" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="105">
+      <c r="A16" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="62">
         <v>123</v>
       </c>
       <c r="H16">
@@ -2462,23 +1992,23 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="112" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="116" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="117" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="118">
+      <c r="A17" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="68"/>
+      <c r="D17" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="69">
         <v>1.2</v>
       </c>
       <c r="H17">
@@ -2489,89 +2019,89 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="119" t="s">
+      <c r="A18" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="72"/>
+      <c r="D18" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="120" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="121"/>
-      <c r="D18" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="123"/>
-      <c r="F18" s="124" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="148" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="149" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" s="149" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="125" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="126" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="127" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="128" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="129" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="130" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="131"/>
+      <c r="D19" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="76"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="132" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="133" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="127" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="134" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="135"/>
-      <c r="F20" s="136" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="137"/>
+      <c r="A20" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="79"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="138" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="139" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="142"/>
-      <c r="F21" s="143" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="144"/>
+      <c r="A21" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="82"/>
+      <c r="D21" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="83"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="148"/>
+  <phoneticPr fontId="87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -2587,23 +2117,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="145" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="146" t="s">
-        <v>76</v>
+      <c r="A1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="330" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="148" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="147" t="s">
-        <v>78</v>
+      <c r="A2" s="87" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="148"/>
+  <phoneticPr fontId="87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
